--- a/剧情.xlsx
+++ b/剧情.xlsx
@@ -1,41 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\我的游戏\Wynne-s-ZOO\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC0FBDE5-4B61-4721-B71D-4EF4BBC79A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="30720" windowHeight="13380" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="序章" sheetId="1" r:id="rId1"/>
     <sheet name="第一章" sheetId="2" r:id="rId2"/>
     <sheet name="第二章" sheetId="4" r:id="rId3"/>
-    <sheet name="解锁顺序" sheetId="3" r:id="rId4"/>
+    <sheet name="第三章" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>wynnm</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>wynnm:</t>
@@ -44,7 +50,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -52,14 +57,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>wynnm:</t>
@@ -68,7 +72,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -89,19 +92,18 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>wynnm</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>wynnm:</t>
@@ -110,7 +112,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -118,14 +119,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>wynnm:</t>
@@ -134,7 +134,68 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1从左到右特写
+2震动
+3镜头拉近
+4双人对话
+5获得物品
+6没有背景（默认在主界面上）
+7互动（扫地）
+8选项
+9解锁动物</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>wynnm</author>
+  </authors>
+  <commentList>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>wynnm:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+对话类型：左=我-生气 右=陆峰</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>wynnm:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -155,7 +216,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="88">
   <si>
     <t>幕</t>
   </si>
@@ -373,7 +434,7 @@
     <t>它看起来受伤了……</t>
   </si>
   <si>
-    <t>1-喂它一点温水 2-帮它清理伤口</t>
+    <t>1-清理污渍 2-涂抹药物</t>
   </si>
   <si>
     <t>第一章-小熊猫-马上干净</t>
@@ -382,10 +443,10 @@
     <t>再喂它一点食物吧……</t>
   </si>
   <si>
-    <t>1-喂它一点食物 2-帮它收拾干净</t>
-  </si>
-  <si>
-    <t>这下好多了！</t>
+    <t>1-喂它一点竹子 2-喂它新鲜的水果</t>
+  </si>
+  <si>
+    <t>小熊猫慢慢放松下来……</t>
   </si>
   <si>
     <t>第一章-小熊猫-干净</t>
@@ -400,25 +461,38 @@
     <t>小熊猫</t>
   </si>
   <si>
-    <t>模块</t>
-  </si>
-  <si>
-    <t>解锁章节-幕</t>
-  </si>
-  <si>
-    <t>解锁小熊猫</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>接入引导</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <t>没有皇位要继承，但我有最纯粹的爱</t>
+  </si>
+  <si>
+    <t>点赞疯狂上涨（用数字跳动表现）</t>
+  </si>
+  <si>
+    <t>第二天，竟然有游客驱车百里赶来，只为看一眼红豆</t>
+  </si>
+  <si>
+    <t>“老板，你这里的动物眼神好有灵气，不像其他地方死气沉沉的。”</t>
+  </si>
+  <si>
+    <t>“因为在这里，它们不是展品，是家人。”</t>
+  </si>
+  <si>
+    <t>【检测到游客增加】建议增加附加收益</t>
+  </si>
+  <si>
+    <t>【盲盒纪念品商店】</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -436,59 +510,371 @@
       <sz val="9"/>
       <color rgb="FF0D0D0D"/>
       <name val="Consolas"/>
-      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
-      <family val="2"/>
-    </font>
-    <font>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -496,9 +882,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -515,24 +1143,68 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -782,19 +1454,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="2" width="13.44140625" customWidth="1"/>
-    <col min="3" max="3" width="54.77734375" customWidth="1"/>
-    <col min="4" max="4" width="31.44140625" customWidth="1"/>
-    <col min="5" max="5" width="23.88671875" customWidth="1"/>
+    <col min="2" max="2" width="13.4444444444444" customWidth="1"/>
+    <col min="3" max="3" width="54.7777777777778" customWidth="1"/>
+    <col min="4" max="4" width="31.4444444444444" customWidth="1"/>
+    <col min="5" max="5" width="23.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1080,7 +1752,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15">
+    <row r="21" ht="15" spans="1:6">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1094,7 +1766,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15">
+    <row r="22" ht="15" spans="1:6">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1185,23 +1857,24 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.77734375" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" customWidth="1"/>
-    <col min="3" max="3" width="55.5546875" customWidth="1"/>
-    <col min="4" max="4" width="23.109375" customWidth="1"/>
-    <col min="5" max="5" width="46.109375" customWidth="1"/>
+    <col min="1" max="1" width="14.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="15.4444444444444" customWidth="1"/>
+    <col min="3" max="3" width="55.5555555555556" customWidth="1"/>
+    <col min="4" max="4" width="23.1111111111111" customWidth="1"/>
+    <col min="5" max="5" width="46.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1332,7 +2005,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="13.05" customHeight="1">
+    <row r="10" ht="13.05" customHeight="1" spans="1:6">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1562,53 +2235,94 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
-  <sheetData/>
-  <phoneticPr fontId="8" type="noConversion"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <cols>
+    <col min="3" max="3" width="63.8888888888889" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="C8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="C9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="C15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="C16" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="12.44140625" customWidth="1"/>
-    <col min="2" max="2" width="26.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="B4" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="B5" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/剧情.xlsx
+++ b/剧情.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380" activeTab="3"/>
+    <workbookView windowWidth="30720" windowHeight="13380" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="序章" sheetId="1" r:id="rId1"/>
     <sheet name="第一章" sheetId="2" r:id="rId2"/>
-    <sheet name="第二章" sheetId="4" r:id="rId3"/>
-    <sheet name="第三章" sheetId="5" r:id="rId4"/>
+    <sheet name="第二章" sheetId="6" r:id="rId3"/>
+    <sheet name="第三章" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -215,8 +215,70 @@
 </comments>
 </file>
 
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>wynnm</author>
+  </authors>
+  <commentList>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>wynnm:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+对话类型：左=我-生气 右=陆峰</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>wynnm:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1从左到右特写
+2震动
+3镜头拉近
+4双人对话
+5获得物品
+6没有背景（默认在主界面上）
+7互动（扫地）
+8选项
+9解锁动物</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="88">
   <si>
     <t>幕</t>
   </si>
@@ -2245,11 +2307,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
-  <cols>
-    <col min="3" max="3" width="63.8888888888889" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
@@ -2269,44 +2328,6 @@
       </c>
       <c r="F1" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="C8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="C9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="C15" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="C16" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="18" spans="3:3">
-      <c r="C18" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="19" spans="3:3">
-      <c r="C19" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -2319,10 +2340,73 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <cols>
+    <col min="3" max="3" width="63.8888888888889" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="C8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="C9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="C15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="C16" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/剧情.xlsx
+++ b/剧情.xlsx
@@ -1,47 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\我的游戏\ZOO\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2ADBD76-39A1-4AA4-AD73-0C274288F278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380" activeTab="2"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="序章" sheetId="1" r:id="rId1"/>
     <sheet name="第一章" sheetId="2" r:id="rId2"/>
     <sheet name="第二章" sheetId="6" r:id="rId3"/>
-    <sheet name="第三章" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>wynnm</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>wynnm:</t>
@@ -50,6 +43,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -57,13 +51,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>wynnm:</t>
@@ -72,6 +67,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -92,18 +88,19 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>wynnm</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>wynnm:</t>
@@ -112,6 +109,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -119,13 +117,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>wynnm:</t>
@@ -134,6 +133,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -154,18 +154,19 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>wynnm</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>wynnm:</t>
@@ -174,6 +175,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -181,13 +183,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>wynnm:</t>
@@ -196,68 +199,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-1从左到右特写
-2震动
-3镜头拉近
-4双人对话
-5获得物品
-6没有背景（默认在主界面上）
-7互动（扫地）
-8选项
-9解锁动物</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>wynnm</author>
-  </authors>
-  <commentList>
-    <comment ref="E1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>wynnm:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-对话类型：左=我-生气 右=陆峰</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>wynnm:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -278,7 +220,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="86">
   <si>
     <t>幕</t>
   </si>
@@ -523,38 +465,30 @@
     <t>小熊猫</t>
   </si>
   <si>
-    <t>没有皇位要继承，但我有最纯粹的爱</t>
-  </si>
-  <si>
-    <t>点赞疯狂上涨（用数字跳动表现）</t>
-  </si>
-  <si>
-    <t>第二天，竟然有游客驱车百里赶来，只为看一眼红豆</t>
-  </si>
-  <si>
-    <t>“老板，你这里的动物眼神好有灵气，不像其他地方死气沉沉的。”</t>
-  </si>
-  <si>
-    <t>“因为在这里，它们不是展品，是家人。”</t>
-  </si>
-  <si>
-    <t>【检测到游客增加】建议增加附加收益</t>
-  </si>
-  <si>
-    <t>【盲盒纪念品商店】</t>
+    <t>我-运动</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>是时候建造一个小熊猫栏舍了！</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击【建造】为红豆修建第一个栖息地</t>
+  </si>
+  <si>
+    <t>旁白</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>主界面</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="26">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -566,377 +500,66 @@
       <sz val="9"/>
       <color rgb="FF0D0D0D"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF0D0D0D"/>
       <name val="Consolas"/>
-      <charset val="134"/>
+      <family val="3"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -944,251 +567,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1205,68 +586,24 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1516,19 +853,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="13.4444444444444" customWidth="1"/>
-    <col min="3" max="3" width="54.7777777777778" customWidth="1"/>
-    <col min="4" max="4" width="31.4444444444444" customWidth="1"/>
-    <col min="5" max="5" width="23.8888888888889" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="3" max="3" width="54.77734375" customWidth="1"/>
+    <col min="4" max="4" width="31.44140625" customWidth="1"/>
+    <col min="5" max="5" width="23.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1807,32 +1144,32 @@
       <c r="B20" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" t="s">
         <v>36</v>
       </c>
       <c r="D20" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="21" ht="15" spans="1:6">
+    <row r="21" spans="1:6" ht="15">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D21" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" ht="15" spans="1:6">
+    <row r="22" spans="1:6" ht="15">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="C22" s="5"/>
+      <c r="C22" s="4"/>
       <c r="D22" t="s">
         <v>23</v>
       </c>
@@ -1919,24 +1256,23 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.7777777777778" customWidth="1"/>
-    <col min="2" max="2" width="15.4444444444444" customWidth="1"/>
-    <col min="3" max="3" width="55.5555555555556" customWidth="1"/>
-    <col min="4" max="4" width="23.1111111111111" customWidth="1"/>
-    <col min="5" max="5" width="46.1111111111111" customWidth="1"/>
+    <col min="1" max="1" width="14.77734375" customWidth="1"/>
+    <col min="2" max="2" width="15.44140625" customWidth="1"/>
+    <col min="3" max="3" width="55.5546875" customWidth="1"/>
+    <col min="4" max="4" width="23.109375" customWidth="1"/>
+    <col min="5" max="5" width="46.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2067,7 +1403,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" ht="13.05" customHeight="1" spans="1:6">
+    <row r="10" spans="1:6" ht="13.05" customHeight="1">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2297,53 +1633,21 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="3" max="3" width="63.8888888888889" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" customWidth="1"/>
+    <col min="3" max="3" width="42.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2366,47 +1670,37 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
-      <c r="C8" t="s">
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>26</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="C9" t="s">
+      <c r="C2" s="5" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="D2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>27</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="C15" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="C16" t="s">
+      <c r="D3" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="3:3">
-      <c r="C18" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="19" spans="3:3">
-      <c r="C19" t="s">
-        <v>87</v>
-      </c>
-    </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/剧情.xlsx
+++ b/剧情.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\我的游戏\ZOO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2ADBD76-39A1-4AA4-AD73-0C274288F278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6661F7ED-5E0E-41ED-9799-DB596ABB78E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="序章" sheetId="1" r:id="rId1"/>
@@ -220,7 +220,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="87">
   <si>
     <t>幕</t>
   </si>
@@ -482,6 +482,9 @@
   <si>
     <t>主界面</t>
     <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>主界面CG</t>
   </si>
 </sst>
 </file>
@@ -1470,7 +1473,7 @@
         <v>63</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1484,7 +1487,7 @@
         <v>65</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1498,7 +1501,7 @@
         <v>66</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1615,7 +1618,7 @@
         <v>78</v>
       </c>
       <c r="D25" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:6">

--- a/剧情.xlsx
+++ b/剧情.xlsx
@@ -1,40 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\我的游戏\ZOO\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6661F7ED-5E0E-41ED-9799-DB596ABB78E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="30720" windowHeight="13380" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="序章" sheetId="1" r:id="rId1"/>
     <sheet name="第一章" sheetId="2" r:id="rId2"/>
     <sheet name="第二章" sheetId="6" r:id="rId3"/>
+    <sheet name="post-build-red-panda" sheetId="7" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>wynnm</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>wynnm:</t>
@@ -43,7 +50,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -51,14 +57,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>wynnm:</t>
@@ -67,7 +72,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -88,19 +92,18 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>wynnm</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>wynnm:</t>
@@ -109,7 +112,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -117,14 +119,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>wynnm:</t>
@@ -133,7 +134,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -154,19 +154,18 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>wynnm</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>wynnm:</t>
@@ -175,7 +174,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -183,14 +181,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>wynnm:</t>
@@ -199,7 +196,68 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1从左到右特写
+2震动
+3镜头拉近
+4双人对话
+5获得物品
+6没有背景（默认在主界面上）
+7互动（扫地）
+8选项
+9解锁动物</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>wynnm</author>
+  </authors>
+  <commentList>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>wynnm:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+对话类型：左=我-生气 右=陆峰</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>wynnm:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -220,7 +278,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="87">
   <si>
     <t>幕</t>
   </si>
@@ -414,84 +472,86 @@
     <t>太棒了！</t>
   </si>
   <si>
+    <t>主界面CG</t>
+  </si>
+  <si>
+    <t>看来也没那么难嘛……</t>
+  </si>
+  <si>
+    <t>此时大福正在远处狂吠不止，像是发现了什么东西。</t>
+  </si>
+  <si>
+    <t>大福发现箱子</t>
+  </si>
+  <si>
+    <t>我急忙打开箱子。</t>
+  </si>
+  <si>
+    <t>第一章-小熊猫</t>
+  </si>
+  <si>
+    <t>是一只小熊猫！</t>
+  </si>
+  <si>
+    <t>它看起来受伤了……</t>
+  </si>
+  <si>
+    <t>1-清理污渍 2-涂抹药物</t>
+  </si>
+  <si>
+    <t>第一章-小熊猫-马上干净</t>
+  </si>
+  <si>
+    <t>再喂它一点食物吧……</t>
+  </si>
+  <si>
+    <t>1-喂它一点竹子 2-喂它新鲜的水果</t>
+  </si>
+  <si>
+    <t>小熊猫慢慢放松下来……</t>
+  </si>
+  <si>
+    <t>第一章-小熊猫-干净</t>
+  </si>
+  <si>
+    <t>你也被抛弃了吗？别怕，以后这里就是你的家。</t>
+  </si>
+  <si>
+    <t>CG-小熊猫</t>
+  </si>
+  <si>
+    <t>小熊猫</t>
+  </si>
+  <si>
+    <t>我-运动</t>
+  </si>
+  <si>
+    <t>是时候建造一个小熊猫栏舍了！</t>
+  </si>
+  <si>
     <t>主界面</t>
   </si>
   <si>
-    <t>看来也没那么难嘛……</t>
-  </si>
-  <si>
-    <t>此时大福正在远处狂吠不止，像是发现了什么东西。</t>
-  </si>
-  <si>
-    <t>大福发现箱子</t>
-  </si>
-  <si>
-    <t>我急忙打开箱子。</t>
-  </si>
-  <si>
-    <t>第一章-小熊猫</t>
-  </si>
-  <si>
-    <t>是一只小熊猫！</t>
-  </si>
-  <si>
-    <t>它看起来受伤了……</t>
-  </si>
-  <si>
-    <t>1-清理污渍 2-涂抹药物</t>
-  </si>
-  <si>
-    <t>第一章-小熊猫-马上干净</t>
-  </si>
-  <si>
-    <t>再喂它一点食物吧……</t>
-  </si>
-  <si>
-    <t>1-喂它一点竹子 2-喂它新鲜的水果</t>
-  </si>
-  <si>
-    <t>小熊猫慢慢放松下来……</t>
-  </si>
-  <si>
-    <t>第一章-小熊猫-干净</t>
-  </si>
-  <si>
-    <t>你也被抛弃了吗？别怕，以后这里就是你的家。</t>
-  </si>
-  <si>
-    <t>CG-小熊猫</t>
-  </si>
-  <si>
-    <t>小熊猫</t>
-  </si>
-  <si>
-    <t>我-运动</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>是时候建造一个小熊猫栏舍了！</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>点击【建造】为红豆修建第一个栖息地</t>
   </si>
   <si>
-    <t>旁白</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>主界面</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>主界面CG</t>
+    <t>太好了</t>
+  </si>
+  <si>
+    <t>真棒</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -500,69 +560,387 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF0D0D0D"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF0D0D0D"/>
       <name val="Consolas"/>
-      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -570,9 +948,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -596,17 +1216,61 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -856,19 +1520,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="2" width="13.44140625" customWidth="1"/>
-    <col min="3" max="3" width="54.77734375" customWidth="1"/>
-    <col min="4" max="4" width="31.44140625" customWidth="1"/>
-    <col min="5" max="5" width="23.88671875" customWidth="1"/>
+    <col min="2" max="2" width="13.4444444444444" customWidth="1"/>
+    <col min="3" max="3" width="54.7777777777778" customWidth="1"/>
+    <col min="4" max="4" width="31.4444444444444" customWidth="1"/>
+    <col min="5" max="5" width="23.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -937,7 +1601,7 @@
       <c r="B5" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D5" t="s">
@@ -1154,25 +1818,25 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15">
+    <row r="21" ht="15" spans="1:6">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D21" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15">
+    <row r="22" ht="15" spans="1:6">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="C22" s="4"/>
+      <c r="C22" s="5"/>
       <c r="D22" t="s">
         <v>23</v>
       </c>
@@ -1259,23 +1923,24 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.77734375" customWidth="1"/>
-    <col min="2" max="2" width="15.44140625" customWidth="1"/>
-    <col min="3" max="3" width="55.5546875" customWidth="1"/>
-    <col min="4" max="4" width="23.109375" customWidth="1"/>
-    <col min="5" max="5" width="46.109375" customWidth="1"/>
+    <col min="1" max="1" width="14.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="15.4444444444444" customWidth="1"/>
+    <col min="3" max="3" width="55.5555555555556" customWidth="1"/>
+    <col min="4" max="4" width="23.1111111111111" customWidth="1"/>
+    <col min="5" max="5" width="46.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1339,7 +2004,7 @@
       <c r="D4" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="1"/>
+      <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
@@ -1382,7 +2047,7 @@
       <c r="D7" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="2"/>
+      <c r="E7" s="3"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
@@ -1406,7 +2071,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="13.05" customHeight="1">
+    <row r="10" ht="13.05" customHeight="1" spans="1:6">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1473,7 +2138,7 @@
         <v>63</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1487,7 +2152,7 @@
         <v>65</v>
       </c>
       <c r="D15" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1501,7 +2166,7 @@
         <v>66</v>
       </c>
       <c r="D16" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1618,7 +2283,7 @@
         <v>78</v>
       </c>
       <c r="D25" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1636,21 +2301,22 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" customWidth="1"/>
-    <col min="3" max="3" width="42.21875" customWidth="1"/>
+    <col min="2" max="2" width="11.5555555555556" customWidth="1"/>
+    <col min="3" max="3" width="42.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1677,33 +2343,94 @@
       <c r="A2">
         <v>26</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
         <v>27</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D3" s="5" t="s">
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>26</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>85</v>
       </c>
+      <c r="D2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>27</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>83</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/剧情.xlsx
+++ b/剧情.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\我的游戏\ZOO\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31A526EF-3A30-42C6-AF42-6D5AF33080FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="序章" sheetId="1" r:id="rId1"/>
@@ -13,35 +19,23 @@
     <sheet name="post-build-red-panda" sheetId="7" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>wynnm</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>wynnm:</t>
@@ -50,6 +44,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -57,13 +52,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>wynnm:</t>
@@ -72,6 +68,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -92,18 +89,19 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>wynnm</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>wynnm:</t>
@@ -112,6 +110,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -119,13 +118,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>wynnm:</t>
@@ -134,6 +134,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -154,18 +155,19 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>wynnm</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>wynnm:</t>
@@ -174,6 +176,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -181,13 +184,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>wynnm:</t>
@@ -196,6 +200,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -216,18 +221,19 @@
 </file>
 
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>wynnm</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>wynnm:</t>
@@ -236,6 +242,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -243,13 +250,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>wynnm:</t>
@@ -258,6 +266,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -278,7 +287,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="94">
   <si>
     <t>幕</t>
   </si>
@@ -484,9 +493,6 @@
     <t>大福发现箱子</t>
   </si>
   <si>
-    <t>我急忙打开箱子。</t>
-  </si>
-  <si>
     <t>第一章-小熊猫</t>
   </si>
   <si>
@@ -508,9 +514,6 @@
     <t>1-喂它一点竹子 2-喂它新鲜的水果</t>
   </si>
   <si>
-    <t>小熊猫慢慢放松下来……</t>
-  </si>
-  <si>
     <t>第一章-小熊猫-干净</t>
   </si>
   <si>
@@ -535,23 +538,51 @@
     <t>点击【建造】为红豆修建第一个栖息地</t>
   </si>
   <si>
-    <t>太好了</t>
-  </si>
-  <si>
-    <t>真棒</t>
+    <t>1-打开箱子</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>箱子里好像有什么东西在动</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>【救助成功】你救下了第一只动物！</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>入住前检查：安全度合格，舒适度合格，清洁度基础，美观度一般</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>栖息地已满足入住条件。</t>
+  </si>
+  <si>
+    <t>现在，让红豆回家吧。</t>
+  </si>
+  <si>
+    <t>小熊猫栖息地剧情CG</t>
+  </si>
+  <si>
+    <t>我-运动</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>【红豆已入住】</t>
+  </si>
+  <si>
+    <t>旁白</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>主界面</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="27">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -576,371 +607,59 @@
       <sz val="9"/>
       <color rgb="FF0D0D0D"/>
       <name val="Consolas"/>
-      <charset val="134"/>
+      <family val="3"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -948,255 +667,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1215,62 +692,21 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1520,19 +956,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="13.4444444444444" customWidth="1"/>
-    <col min="3" max="3" width="54.7777777777778" customWidth="1"/>
-    <col min="4" max="4" width="31.4444444444444" customWidth="1"/>
-    <col min="5" max="5" width="23.8888888888889" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="3" max="3" width="54.77734375" customWidth="1"/>
+    <col min="4" max="4" width="31.44140625" customWidth="1"/>
+    <col min="5" max="5" width="23.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1818,7 +1254,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" ht="15" spans="1:6">
+    <row r="21" spans="1:6" ht="15">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1832,7 +1268,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" ht="15" spans="1:6">
+    <row r="22" spans="1:6" ht="15">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1923,24 +1359,23 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.7777777777778" customWidth="1"/>
-    <col min="2" max="2" width="15.4444444444444" customWidth="1"/>
-    <col min="3" max="3" width="55.5555555555556" customWidth="1"/>
-    <col min="4" max="4" width="23.1111111111111" customWidth="1"/>
-    <col min="5" max="5" width="46.1111111111111" customWidth="1"/>
+    <col min="1" max="1" width="14.77734375" customWidth="1"/>
+    <col min="2" max="2" width="15.44140625" customWidth="1"/>
+    <col min="3" max="3" width="55.5546875" customWidth="1"/>
+    <col min="4" max="4" width="23.109375" customWidth="1"/>
+    <col min="5" max="5" width="46.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2071,7 +1506,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" ht="13.05" customHeight="1" spans="1:6">
+    <row r="10" spans="1:6" ht="13.05" customHeight="1">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2184,11 +1619,17 @@
       <c r="B18" t="s">
         <v>8</v>
       </c>
-      <c r="C18" t="s">
-        <v>68</v>
+      <c r="C18" s="6" t="s">
+        <v>84</v>
       </c>
       <c r="D18" t="s">
         <v>67</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F18">
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2196,7 +1637,7 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E19" t="s">
         <v>52</v>
@@ -2213,10 +1654,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -2227,10 +1668,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="s">
+        <v>70</v>
+      </c>
+      <c r="E21" t="s">
         <v>71</v>
-      </c>
-      <c r="E21" t="s">
-        <v>72</v>
       </c>
       <c r="F21">
         <v>8</v>
@@ -2241,7 +1682,7 @@
         <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -2249,10 +1690,10 @@
         <v>22</v>
       </c>
       <c r="C23" t="s">
+        <v>73</v>
+      </c>
+      <c r="E23" t="s">
         <v>74</v>
-      </c>
-      <c r="E23" t="s">
-        <v>75</v>
       </c>
       <c r="F23">
         <v>8</v>
@@ -2265,11 +1706,11 @@
       <c r="B24" t="s">
         <v>8</v>
       </c>
-      <c r="C24" t="s">
-        <v>76</v>
+      <c r="C24" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="D24" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -2280,7 +1721,7 @@
         <v>57</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D25" t="s">
         <v>64</v>
@@ -2291,32 +1732,31 @@
         <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E26" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F26">
         <v>9</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="11.5555555555556" customWidth="1"/>
-    <col min="3" max="3" width="42.2222222222222" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" customWidth="1"/>
+    <col min="3" max="3" width="42.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2344,13 +1784,13 @@
         <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" t="s">
         <v>81</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D2" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2361,24 +1801,30 @@
         <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="19.33203125" customWidth="1"/>
+    <col min="3" max="3" width="45.5546875" customWidth="1"/>
+    <col min="4" max="4" width="32.88671875" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
@@ -2404,33 +1850,69 @@
       <c r="A2">
         <v>26</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" t="s">
         <v>81</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D2" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
         <v>27</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>86</v>
+      <c r="B3" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>28</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>30</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>